--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N28_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N28_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.22679613093974</v>
+        <v>6.211854371277708</v>
       </c>
       <c r="D2" t="n">
-        <v>17.8916811426529</v>
+        <v>2.907398185681096</v>
       </c>
       <c r="E2" t="n">
-        <v>11.76869889399424</v>
+        <v>1.912413570274064</v>
       </c>
       <c r="F2" t="n">
-        <v>12.41003163374761</v>
+        <v>2.016630140483987</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.43239811186393</v>
+        <v>4.295264693177889</v>
       </c>
       <c r="D3" t="n">
-        <v>25.34923364406436</v>
+        <v>4.119250467160459</v>
       </c>
       <c r="E3" t="n">
-        <v>11.76869889399424</v>
+        <v>1.912413570274064</v>
       </c>
       <c r="F3" t="n">
-        <v>12.41003163374761</v>
+        <v>2.016630140483987</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>54.99349234539031</v>
+        <v>8.936442506125925</v>
       </c>
       <c r="D4" t="n">
-        <v>38.33887045294428</v>
+        <v>6.230066448603445</v>
       </c>
       <c r="E4" t="n">
-        <v>11.76869889399424</v>
+        <v>1.912413570274064</v>
       </c>
       <c r="F4" t="n">
-        <v>12.41003163374761</v>
+        <v>2.016630140483987</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.66782068038831</v>
+        <v>6.446020860563101</v>
       </c>
       <c r="D5" t="n">
-        <v>33.29855860397024</v>
+        <v>5.411015773145165</v>
       </c>
       <c r="E5" t="n">
-        <v>11.76869889399424</v>
+        <v>1.912413570274064</v>
       </c>
       <c r="F5" t="n">
-        <v>12.41003163374761</v>
+        <v>2.016630140483987</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.87086342139676</v>
+        <v>6.804015305976973</v>
       </c>
       <c r="D6" t="n">
-        <v>40.05281084239233</v>
+        <v>6.508581761888753</v>
       </c>
       <c r="E6" t="n">
-        <v>11.76869889399424</v>
+        <v>1.912413570274064</v>
       </c>
       <c r="F6" t="n">
-        <v>12.41003163374761</v>
+        <v>2.016630140483987</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>36.9428845983265</v>
+        <v>6.003218747228057</v>
       </c>
       <c r="D7" t="n">
-        <v>36.72699339454468</v>
+        <v>5.96813642661351</v>
       </c>
       <c r="E7" t="n">
-        <v>11.76869889399424</v>
+        <v>1.912413570274064</v>
       </c>
       <c r="F7" t="n">
-        <v>12.41003163374761</v>
+        <v>2.016630140483987</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>37.71330815772867</v>
+        <v>6.128412575630909</v>
       </c>
       <c r="D8" t="n">
-        <v>35.35099305733718</v>
+        <v>5.744536371817292</v>
       </c>
       <c r="E8" t="n">
-        <v>11.76869889399424</v>
+        <v>1.912413570274064</v>
       </c>
       <c r="F8" t="n">
-        <v>12.41003163374761</v>
+        <v>2.016630140483987</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>43.4175018162279</v>
+        <v>7.055344045137034</v>
       </c>
       <c r="D9" t="n">
-        <v>43.1760384426719</v>
+        <v>7.016106246934185</v>
       </c>
       <c r="E9" t="n">
-        <v>11.76869889399424</v>
+        <v>1.912413570274064</v>
       </c>
       <c r="F9" t="n">
-        <v>12.41003163374761</v>
+        <v>2.016630140483987</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>23.65726475771528</v>
+        <v>3.844305523128733</v>
       </c>
       <c r="D10" t="n">
-        <v>22.71848970858755</v>
+        <v>3.691754577645477</v>
       </c>
       <c r="E10" t="n">
-        <v>11.76869889399424</v>
+        <v>1.912413570274064</v>
       </c>
       <c r="F10" t="n">
-        <v>12.41003163374761</v>
+        <v>2.016630140483987</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>12.42158548381573</v>
+        <v>2.018507641120056</v>
       </c>
       <c r="D11" t="n">
-        <v>8.287944375287372</v>
+        <v>1.346790960984198</v>
       </c>
       <c r="E11" t="n">
-        <v>11.76869889399424</v>
+        <v>1.912413570274064</v>
       </c>
       <c r="F11" t="n">
-        <v>12.41003163374761</v>
+        <v>2.016630140483987</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>29.73816348779605</v>
+        <v>4.832451566766859</v>
       </c>
       <c r="D12" t="n">
-        <v>58.0598573469501</v>
+        <v>9.434726818879392</v>
       </c>
       <c r="E12" t="n">
-        <v>11.76869889399424</v>
+        <v>1.912413570274064</v>
       </c>
       <c r="F12" t="n">
-        <v>12.41003163374761</v>
+        <v>2.016630140483987</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>15.15287350856575</v>
+        <v>2.462341945141934</v>
       </c>
       <c r="D13" t="n">
-        <v>28.36639543093068</v>
+        <v>4.609539257526235</v>
       </c>
       <c r="E13" t="n">
-        <v>11.76869889399424</v>
+        <v>1.912413570274064</v>
       </c>
       <c r="F13" t="n">
-        <v>12.41003163374761</v>
+        <v>2.016630140483987</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
